--- a/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2477</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>3889</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3506</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3199</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4840</t>
+          <t>4576</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,15%</t>
         </is>
       </c>
     </row>
@@ -1413,7 +1413,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5625</t>
+          <t>5629</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>476</t>
+          <t>491</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>6735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2771</t>
+          <t>2610</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>2214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>370</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1336</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5806</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1174</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>6129</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>517</t>
+          <t>542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4751</t>
+          <t>4756</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1782,12 +1782,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1997</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -1860,12 +1860,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19909</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26653</t>
+          <t>26717</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,46%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1895,12 +1895,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14440</t>
+          <t>14000</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20891</t>
+          <t>20722</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,71%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1930,12 +1930,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36406</t>
+          <t>36498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>46361</t>
+          <t>45740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>81,46%</t>
         </is>
       </c>
     </row>
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>960</t>
+          <t>953</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9941</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,77%</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1419</t>
+          <t>1444</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1812</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10257</t>
+          <t>9966</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4725</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>2891</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>428</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>414</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7282</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4377</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>2387</t>
+          <t>3155</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>478</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -2994,12 +2994,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>5859</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2128</t>
+          <t>2252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9575</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13384</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -3107,12 +3107,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15024</t>
+          <t>14681</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3142,12 +3142,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4390</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>12638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3177,12 +3177,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>12189</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23792</t>
+          <t>24484</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>50897</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62696</t>
+          <t>63052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66635</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>81952</t>
+          <t>80769</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122660</t>
+          <t>122802</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>140178</t>
+          <t>140735</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,62%</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2154</t>
+          <t>2118</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>426</t>
+          <t>431</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t>7820</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6241</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>5731</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3488</t>
+          <t>3737</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>4237</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -3942,7 +3942,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>5663</t>
+          <t>5488</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>798</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -4128,12 +4128,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1950</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4143,12 +4143,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>17031</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21723</t>
+          <t>20476</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,13%</t>
         </is>
       </c>
     </row>
@@ -4246,7 +4246,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>5312</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4283</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4311,12 +4311,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>703</t>
+          <t>676</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>3692</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4404,12 +4404,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>6844</t>
+          <t>7024</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21341</t>
+          <t>21838</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4439,12 +4439,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -4467,12 +4467,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>9688</t>
+          <t>10042</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>21854</t>
+          <t>22011</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>6860</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>18617</t>
+          <t>17651</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4517,12 +4517,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>19441</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35505</t>
+          <t>35992</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4552,12 +4552,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,8%</t>
         </is>
       </c>
     </row>
@@ -4580,12 +4580,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>48234</t>
+          <t>48071</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>63973</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>57,2%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>72151</t>
+          <t>72915</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91963</t>
+          <t>91462</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>126089</t>
+          <t>125564</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>151243</t>
+          <t>150385</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4665,12 +4665,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,1%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2527</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4887</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>4256</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4993,12 +4993,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>413</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>6394</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>2540</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>9996</t>
+          <t>8752</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>5869</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -5488,12 +5488,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9922</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>769</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7371</t>
+          <t>7677</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5538,12 +5538,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>2100</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>11837</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -5601,12 +5601,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>676</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>7276</t>
+          <t>6611</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5616,12 +5616,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5636,12 +5636,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>487</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5651,12 +5651,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1906</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>11077</t>
+          <t>10958</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5686,12 +5686,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -5714,12 +5714,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>13321</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5729,12 +5729,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>9694</t>
+          <t>10132</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5764,12 +5764,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>19479</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5799,12 +5799,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -5827,12 +5827,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>17979</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>14934</t>
+          <t>15209</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>36932</t>
+          <t>37686</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5877,12 +5877,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22742</t>
+          <t>22699</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>51165</t>
+          <t>50850</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5912,12 +5912,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105050</t>
+          <t>105396</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>128146</t>
+          <t>128766</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>93595</t>
+          <t>92909</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>116479</t>
+          <t>116046</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5990,12 +5990,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>205136</t>
+          <t>206010</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>242317</t>
+          <t>243005</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6025,12 +6025,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,8%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,7%</t>
         </is>
       </c>
     </row>
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>428</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5694</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2482</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>12752</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3611</t>
+          <t>3615</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>15821</t>
+          <t>14409</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6260,7 +6260,7 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6283,12 +6283,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>409</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6318,12 +6318,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>3821</t>
+          <t>3974</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>14013</t>
+          <t>13975</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6333,12 +6333,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6353,12 +6353,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5261</t>
+          <t>5435</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>16990</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6368,12 +6368,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6436,7 +6436,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>6611</t>
+          <t>6545</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1996</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>396</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4912</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>2073</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>10694</t>
+          <t>11398</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6672,12 +6672,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1763</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11206</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>738</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>6936</t>
+          <t>7286</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -6750,82 +6750,82 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>4906</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>1770</t>
+        </is>
+      </c>
+      <c r="T57" s="2" t="inlineStr">
+        <is>
+          <t>10347</t>
+        </is>
+      </c>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
           <t>0,25%</t>
         </is>
       </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>1956</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>6565</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,51%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>4906</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>2168</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>11313</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6848,12 +6848,12 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>6703</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>19796</t>
+          <t>19007</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -6863,12 +6863,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>6568</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>22260</t>
+          <t>20672</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -6898,12 +6898,12 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>14918</t>
+          <t>15635</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>34706</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -6961,12 +6961,12 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>2949</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>11148</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
@@ -6976,12 +6976,12 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10128</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7011,12 +7011,12 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>17179</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -7074,12 +7074,12 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>8499</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>21170</t>
+          <t>21682</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -7089,12 +7089,12 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>30583</t>
+          <t>31102</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7124,12 +7124,12 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>46912</t>
+          <t>46954</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -7159,7 +7159,7 @@
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>26864</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>49281</t>
+          <t>48455</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -7202,12 +7202,12 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33649</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>63238</t>
+          <t>61424</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7237,12 +7237,12 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>68161</t>
+          <t>66697</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>103351</t>
+          <t>100708</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,03%</t>
         </is>
       </c>
     </row>
@@ -7300,12 +7300,12 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7315,12 +7315,12 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7350,12 +7350,12 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7370,12 +7370,12 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>382</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>382</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -805,12 +805,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>1870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -833,82 +833,82 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3154</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>5,34%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>15,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3889</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>14,84%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1344</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>4033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1059,82 +1059,82 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>323</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1634</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>6,23%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>323</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1654</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1172,82 +1172,82 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2671</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2,99%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3100</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>626</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>1332</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>4141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,83%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4351</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4576</t>
+          <t>4542</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1398,47 +1398,47 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2108</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1639</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5629</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>479</t>
+          <t>1441</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>4789</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2119</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>399</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6735</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -1511,47 +1511,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1792</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>8,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2610</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>685</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2174</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>983</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>292</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>3237</t>
+          <t>2792</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1624,107 +1624,107 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>987</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4812</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>11,49%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>2996</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>1453</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>5968</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>6129</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1737,72 +1737,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4038</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>19,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1939</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>542</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4756</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>6,47%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1861</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4432</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>6,87%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>15,88%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>762</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>4834</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>2,91%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4069</t>
+          <t>3679</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1717</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1850,72 +1850,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>13964</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>10994</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16675</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>66,63%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>52,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>79,57%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23780</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>19909</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26717</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>79,41%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>66,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>89,21%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17843</t>
+          <t>21410</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14000</t>
+          <t>17796</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20722</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41623</t>
+          <t>35374</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36498</t>
+          <t>31280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45740</t>
+          <t>38906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -1963,74 +1963,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>20956</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29947</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>27085</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>26208</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>110</t>
@@ -2038,17 +2038,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>48041</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2080,107 +2080,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>7070</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>8,38%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>3481</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9185</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,56%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>9,39%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3481</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>877</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>7503</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -2193,72 +2193,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3531</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7384</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4,18%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>8,75%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>4331</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>5,81%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>4047</t>
+          <t>860</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1444</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9633</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4870</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1946</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>9966</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -2306,82 +2306,82 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>945</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5422</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5275</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>5,39%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>945</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4782</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>365</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2009</t>
+          <t>2075</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>849</t>
+          <t>724</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2891</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>329</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5962</t>
+          <t>3065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,32 +2798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>360</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>5717</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,32 +2833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7282</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -2871,47 +2871,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1779</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>3860</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>470</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3155</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1694</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>353</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -2984,72 +2984,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>3638</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>7223</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,56%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>2646</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1041</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>6255</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4860</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2252</t>
+          <t>845</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9575</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>7505</t>
+          <t>6076</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>3457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>13369</t>
+          <t>10804</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -3097,72 +3097,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6962</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3736</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11295</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,38%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>9982</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>5911</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>14681</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,69%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4404</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12638</t>
+          <t>14873</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>17646</t>
+          <t>16934</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>11362</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24484</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>15,06%</t>
         </is>
       </c>
     </row>
@@ -3210,72 +3210,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>64630</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>57724</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>70074</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>76,59%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>68,4%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>83,04%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>57523</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>52047</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>63052</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>77,14%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>69,79%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>84,55%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>74581</t>
+          <t>51143</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>66534</t>
+          <t>45720</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>80769</t>
+          <t>56358</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>76,22%</t>
+          <t>75,54%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3285,32 +3285,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>132104</t>
+          <t>115773</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>122802</t>
+          <t>106647</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>140735</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>70,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -3323,74 +3323,74 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>84390</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>74574</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>67700</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="P27" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>97845</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
           <t>274</t>
@@ -3398,17 +3398,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>172419</t>
+          <t>152089</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3440,47 +3440,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,51%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>366</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,12 +3490,12 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>7573</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2526</t>
+          <t>2336</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>431</t>
+          <t>367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -3553,82 +3553,82 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>7334</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6,48%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>6571</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>1,54%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1813</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -3638,12 +3638,12 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5731</t>
+          <t>6487</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -3666,82 +3666,82 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>961</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>5448</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>4679</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>961</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -3779,72 +3779,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>835</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>3737</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>866</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3939</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>866</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -3892,82 +3892,82 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>962</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>4874</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>4145</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>937</t>
+          <t>962</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -4005,47 +4005,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>5159</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>1619</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>5488</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>6,51%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>1731</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4080,32 +4080,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>2562</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>798</t>
+          <t>856</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>7873</t>
+          <t>7839</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
     </row>
@@ -4118,72 +4118,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>6025</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2575</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>11756</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>10,39%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>4758</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>1717</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>9500</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>11,27%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>7432</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2944</t>
+          <t>2151</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4193,32 +4193,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>12190</t>
+          <t>10857</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>5795</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -4231,47 +4231,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>1436</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>5312</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>6,3%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4309</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,22 +4306,22 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>652</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>6077</t>
+          <t>6067</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -4344,72 +4344,72 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>8311</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>16151</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>7,35%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>14,28%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>3908</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1433</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>8248</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>8500</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4045</t>
+          <t>1346</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>12407</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>7024</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21838</t>
+          <t>20454</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -4457,72 +4457,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11790</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>7152</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>18758</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>16,58%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>14912</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>10042</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>22011</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>17,68%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>11758</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>22321</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4532,32 +4532,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>26669</t>
+          <t>27590</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>18519</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>35992</t>
+          <t>36952</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,72%</t>
         </is>
       </c>
     </row>
@@ -4570,72 +4570,72 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>79364</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>69969</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>88781</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>70,15%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>61,85%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>56431</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>48071</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>63113</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>66,92%</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>57,01%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>74,85%</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>82506</t>
+          <t>55703</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>72915</t>
+          <t>48060</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>91462</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>77,59%</t>
+          <t>74,35%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4645,32 +4645,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>138936</t>
+          <t>135067</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>125564</t>
+          <t>124000</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>150385</t>
+          <t>146585</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>74,37%</t>
+          <t>74,28%</t>
         </is>
       </c>
     </row>
@@ -4683,74 +4683,74 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>113132</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>84320</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>84213</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
+      <c r="P39" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>117881</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>251</t>
@@ -4758,17 +4758,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>202200</t>
+          <t>197346</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>360</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -4815,12 +4815,12 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>2189</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>439</t>
+          <t>751</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>3793</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,42 +4865,42 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>4136</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>1,58%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>1156</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>3866</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -4913,47 +4913,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>4391</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>1132</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>4256</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
@@ -4978,7 +4978,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,22 +4988,22 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>356</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -5139,72 +5139,72 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>2411</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>2115</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>405</t>
+          <t>342</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,66%</t>
         </is>
       </c>
     </row>
@@ -5252,82 +5252,82 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>7417</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>5,32%</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J44" s="2" t="inlineStr">
+      <c r="Q44" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>2548</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr">
-        <is>
-          <t>8799</t>
-        </is>
-      </c>
-      <c r="N44" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="O44" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P44" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="Q44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>9838</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,77%</t>
         </is>
       </c>
     </row>
@@ -5365,82 +5365,82 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>988</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I45" s="2" t="inlineStr">
+      <c r="P45" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J45" s="2" t="inlineStr">
+      <c r="Q45" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>1012</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr">
-        <is>
-          <t>5100</t>
-        </is>
-      </c>
-      <c r="N45" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O45" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P45" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="Q45" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>988</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>5406</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5465,7 +5465,7 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>827</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>2619</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>769</t>
+          <t>785</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>7677</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>5763</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>2100</t>
+          <t>2564</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -5591,72 +5591,72 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>2468</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>430</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>7828</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>5,61%</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>2605</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>6611</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>2710</t>
+          <t>2809</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>784</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5277</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>10733</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>4,11%</t>
         </is>
       </c>
     </row>
@@ -5704,72 +5704,72 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>4712</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>9785</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>7,01%</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>7337</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>3175</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>13321</t>
-        </is>
-      </c>
-      <c r="G48" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="inlineStr">
-        <is>
-          <t>9,33%</t>
-        </is>
-      </c>
-      <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>10132</t>
+          <t>13022</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5779,32 +5779,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>12028</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>6708</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>19491</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -5817,72 +5817,72 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>22118</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>15051</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>35498</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>15,86%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>25,45%</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>11422</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>5505</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>18454</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>8,0%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
-        <is>
-          <t>12,93%</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>22584</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15209</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>37686</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5892,32 +5892,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>34005</t>
+          <t>34189</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22699</t>
+          <t>25276</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>50850</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,83%</t>
         </is>
       </c>
     </row>
@@ -5935,32 +5935,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>115941</t>
+          <t>102781</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>105396</t>
+          <t>89630</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>128766</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>73,69%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5970,32 +5970,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>106760</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>92909</t>
+          <t>85310</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>116046</t>
+          <t>101047</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>74,03%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6005,32 +6005,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>222701</t>
+          <t>196221</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>206010</t>
+          <t>181721</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>243005</t>
+          <t>208671</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>79,87%</t>
         </is>
       </c>
     </row>
@@ -6043,74 +6043,74 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>139486</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>142702</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>121771</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I51" s="2" t="inlineStr">
+      <c r="P51" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>144216</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
           <t>344</t>
@@ -6118,17 +6118,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>286918</t>
+          <t>261257</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6160,72 +6160,72 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>5178</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>10988</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>428</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>5694</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2482</t>
+          <t>368</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>6677</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>3615</t>
+          <t>2859</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>14409</t>
+          <t>12287</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -6273,72 +6273,72 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>3802</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>14168</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>3,96%</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>1954</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>409</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>5941</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>1970</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>363</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5956</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>0,65%</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>0,12%</t>
         </is>
       </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,79%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>8058</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>3974</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>13975</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>10012</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>5435</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>16925</t>
+          <t>16217</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -6386,82 +6386,82 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>1915</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>6545</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>1915</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -6499,47 +6499,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>2122</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>1240</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>4884</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
@@ -6564,7 +6564,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6574,17 +6574,17 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>1631</t>
+          <t>1530</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>396</t>
+          <t>326</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>4912</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6594,12 +6594,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -6612,72 +6612,72 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>4483</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>12222</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>1,25%</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>359</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,22 +6687,22 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>4964</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1671</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>11543</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -6712,7 +6712,7 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -6725,72 +6725,72 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>1946</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>6644</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>2951</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>738</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>7286</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>868</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>4906</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>10906</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>19007</t>
+          <t>16953</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>11901</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>19563</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,32 +6913,32 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>23404</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>15635</t>
+          <t>15007</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>31373</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -6951,107 +6951,107 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>4046</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>1397</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>9413</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>6060</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>2949</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>11723</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>5849</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>2970</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>10158</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>3,38%</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>9895</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>5844</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>17011</t>
+        </is>
+      </c>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>4487</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>1383</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>10128</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>10547</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>6064</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>17179</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -7064,72 +7064,72 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>19070</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>12017</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>26732</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>5,33%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>7,47%</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>13890</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>8499</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>21682</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>6,54%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>21046</t>
+          <t>13763</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>31102</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7139,32 +7139,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>34936</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>25023</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>46954</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -7182,32 +7182,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>42688</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>26864</t>
+          <t>32877</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>48455</t>
+          <t>58895</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -7217,32 +7217,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>44135</t>
+          <t>39704</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>30752</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>61424</t>
+          <t>50121</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7252,32 +7252,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>82389</t>
+          <t>82392</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>66697</t>
+          <t>69848</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>100708</t>
+          <t>99588</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -7290,72 +7290,72 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>253675</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>239906</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>273005</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7365,32 +7365,32 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>461960</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>560991</t>
+          <t>501963</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -7403,74 +7403,74 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>300769</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I63" s="2" t="inlineStr">
+      <c r="P63" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>386149</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
           <t>979</t>
@@ -7478,17 +7478,17 @@
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T63" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U63" s="2" t="inlineStr">
